--- a/public/assets/sample/sample.xlsx
+++ b/public/assets/sample/sample.xlsx
@@ -1148,6 +1148,23 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -1165,23 +1182,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1196,7 +1196,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="XEX1:XEZ94" totalsRowShown="0" headerRowDxfId="1" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="XEX1:XEZ94" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 2">
   <autoFilter ref="XEX1:XEZ94"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Product ID"/>
@@ -7603,7 +7603,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2 J3:L998 B1 C1:U2">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$J1&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7627,7 +7627,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$XER$2:$XER$4</xm:f>
           </x14:formula1>
-          <xm:sqref>B2</xm:sqref>
+          <xm:sqref>B2:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
